--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486539_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486539_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. BARRO</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6036</v>
+        <v>5.0527</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4071</v>
+        <v>5.4388</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1965</v>
+        <v>-0.3861</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2311</v>
+        <v>2.3772</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0646</v>
+        <v>0.511</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2957</v>
+        <v>1.8662</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7062</v>
+        <v>4.5289</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5149</v>
+        <v>1.0283</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1912</v>
+        <v>3.5006</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9372</v>
+        <v>-2.1517</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4504</v>
+        <v>-0.5173</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4869</v>
+        <v>-1.6344</v>
       </c>
       <c r="P2" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6395</v>
+        <v>1.0229</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3758</v>
+        <v>0.3449</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2637</v>
+        <v>0.678</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3252</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3252</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>S. BARRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4014</v>
+        <v>3.4957</v>
       </c>
       <c r="E3" t="n">
-        <v>4.88</v>
+        <v>2.7307</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4786</v>
+        <v>0.7649</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3772</v>
+        <v>-0.2311</v>
       </c>
       <c r="H3" t="n">
-        <v>0.511</v>
+        <v>0.0646</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8662</v>
+        <v>-0.2957</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5289</v>
+        <v>0.7062</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0283</v>
+        <v>0.5149</v>
       </c>
       <c r="L3" t="n">
-        <v>3.5006</v>
+        <v>0.1912</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.1517</v>
+        <v>-0.9372</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5173</v>
+        <v>-0.4504</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6344</v>
+        <v>-0.4869</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3717</v>
+        <v>1.5316</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2139</v>
+        <v>0.6994</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5856</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.3252</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.3252</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9632</v>
+        <v>3.3429</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7396</v>
+        <v>2.2119</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2235</v>
+        <v>1.1311</v>
       </c>
       <c r="G4" t="n">
         <v>-0.6022</v>
@@ -766,13 +766,13 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7399</v>
+        <v>1.1197</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0036</v>
+        <v>0.4759</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7363</v>
+        <v>0.6438</v>
       </c>
       <c r="V4" t="n">
         <v>1.5204</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7355</v>
+        <v>1.7963</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5337</v>
+        <v>1.3787</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2018</v>
+        <v>0.4175</v>
       </c>
       <c r="G5" t="n">
         <v>1.0743</v>
@@ -844,13 +844,13 @@
         <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2039</v>
+        <v>0.2647</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3581</v>
+        <v>0.2031</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1542</v>
+        <v>0.0616</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1952</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9154</v>
+        <v>0.5099</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8282</v>
+        <v>1.1144</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9127999999999999</v>
+        <v>-0.6045</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2203</v>
@@ -922,13 +922,13 @@
         <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7437</v>
+        <v>1.3381</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6187</v>
+        <v>0.9049</v>
       </c>
       <c r="U6" t="n">
-        <v>0.125</v>
+        <v>0.4332</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3904</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2944</v>
+        <v>-0.0687</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6041</v>
+        <v>-0.5356</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8984</v>
+        <v>0.4669</v>
       </c>
       <c r="G7" t="n">
         <v>-2.6526</v>
@@ -1000,13 +1000,13 @@
         <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6218</v>
+        <v>1.2588</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2776</v>
+        <v>0.3461</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3442</v>
+        <v>0.9127</v>
       </c>
       <c r="V7" t="n">
         <v>1.3252</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2956</v>
+        <v>-0.3734</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8837</v>
+        <v>-0.5917</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5881</v>
+        <v>0.2182</v>
       </c>
       <c r="G8" t="n">
         <v>-2.039</v>
@@ -1078,13 +1078,13 @@
         <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0909</v>
+        <v>1.013</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0649</v>
+        <v>0.2271</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1558</v>
+        <v>0.7859</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1467</v>
+        <v>-0.5819</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3</v>
+        <v>-1.8278</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1534</v>
+        <v>1.2458</v>
       </c>
       <c r="G9" t="n">
         <v>1.3348</v>
@@ -1156,13 +1156,13 @@
         <v>1.5225</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7382</v>
+        <v>1.3029</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2211</v>
+        <v>0.6934</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5171</v>
+        <v>0.6096</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1745</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7767</v>
+        <v>-1.1062</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8812</v>
+        <v>-0.2107</v>
       </c>
       <c r="F10" t="n">
         <v>-0.8955</v>
@@ -1234,10 +1234,10 @@
         <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0565</v>
+        <v>0.727</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6165</v>
+        <v>0.0541</v>
       </c>
       <c r="U10" t="n">
         <v>0.6729000000000001</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0626</v>
+        <v>-1.9104</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.77</v>
+        <v>0.0124</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2926</v>
+        <v>-1.9227</v>
       </c>
       <c r="G11" t="n">
         <v>0.2459</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8734</v>
+        <v>0.2788</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9589</v>
+        <v>-0.1766</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0856</v>
+        <v>0.4554</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2598</v>
+        <v>-3.0997</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.131</v>
+        <v>-2.2175</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1288</v>
+        <v>-0.8822</v>
       </c>
       <c r="G12" t="n">
         <v>-3.6028</v>
@@ -1390,13 +1390,13 @@
         <v>1.7401</v>
       </c>
       <c r="S12" t="n">
-        <v>1.038</v>
+        <v>1.1981</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7607</v>
+        <v>0.6742</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2773</v>
+        <v>0.5239</v>
       </c>
       <c r="V12" t="n">
         <v>-1.13</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.3721</v>
+        <v>7.0572</v>
       </c>
       <c r="E13" t="n">
-        <v>6.818599999999998</v>
+        <v>7.5036</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.446600000000001</v>
+        <v>-0.4466000000000002</v>
       </c>
       <c r="G13" t="n">
         <v>-6.780799999999999</v>
@@ -1468,13 +1468,13 @@
         <v>11.9626</v>
       </c>
       <c r="S13" t="n">
-        <v>10.3707</v>
+        <v>11.0556</v>
       </c>
       <c r="T13" t="n">
-        <v>3.7614</v>
+        <v>4.4465</v>
       </c>
       <c r="U13" t="n">
-        <v>6.609300000000001</v>
+        <v>6.609200000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.695</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9412</v>
+        <v>6.5129</v>
       </c>
       <c r="E14" t="n">
-        <v>5.6225</v>
+        <v>5.9578</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3187</v>
+        <v>0.5551</v>
       </c>
       <c r="G14" t="n">
         <v>6.6265</v>
@@ -1546,13 +1546,13 @@
         <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.9903</v>
+        <v>-1.4186</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3014</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6888</v>
+        <v>-0.4525</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>I. ARROYO VARELA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7347</v>
+        <v>1.2407</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2637</v>
+        <v>0.258</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5291</v>
+        <v>0.9827</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8411999999999999</v>
+        <v>3.2707</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.7393</v>
+        <v>2.077</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8981</v>
+        <v>1.1937</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4586</v>
+        <v>3.4677</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8419</v>
+        <v>1.9162</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3005</v>
+        <v>1.5515</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2998</v>
+        <v>-0.197</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8974</v>
+        <v>0.1608</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4024</v>
+        <v>-0.3578</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0875</v>
+        <v>-0.435</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2486</v>
+        <v>-1.595</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8051</v>
+        <v>-1.0346</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4434</v>
+        <v>-0.5603</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6817</v>
+        <v>0.7023</v>
       </c>
       <c r="E16" t="n">
         <v>2.1991</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5175</v>
+        <v>-1.4969</v>
       </c>
       <c r="G16" t="n">
         <v>2.7962</v>
@@ -1702,13 +1702,13 @@
         <v>0.6525</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8976</v>
+        <v>-0.8769</v>
       </c>
       <c r="T16" t="n">
         <v>-0.9589</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0614</v>
+        <v>0.082</v>
       </c>
       <c r="V16" t="n">
         <v>-1.8695</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. ARROYO VARELA</t>
+          <t>A. ANABITARTE SOROA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.2004</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6796</v>
+        <v>0.2004</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2707</v>
+        <v>0.149</v>
       </c>
       <c r="H17" t="n">
-        <v>2.077</v>
+        <v>0.149</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1937</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4677</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9162</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5515</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.197</v>
+        <v>0.149</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1608</v>
+        <v>0.149</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3578</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.435</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.2334</v>
+        <v>0.0514</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3699</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8633999999999999</v>
+        <v>0.0514</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4288</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1897</v>
+        <v>0.0779</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2391</v>
+        <v>-0.1616</v>
       </c>
       <c r="G18" t="n">
         <v>-2.4201</v>
@@ -1858,13 +1858,13 @@
         <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0412</v>
+        <v>-0.5537</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2139</v>
+        <v>-0.3256</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1727</v>
+        <v>-0.228</v>
       </c>
       <c r="V18" t="n">
         <v>2.4552</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ANABITARTE SOROA</t>
+          <t>M. ANSORREGUI DEBA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1696</v>
+        <v>-0.235</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-0.73</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1696</v>
+        <v>0.495</v>
       </c>
       <c r="G19" t="n">
-        <v>0.149</v>
+        <v>-0.4769</v>
       </c>
       <c r="H19" t="n">
-        <v>0.149</v>
+        <v>0.7693</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-1.2463</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.7608</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.9886</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.2279</v>
       </c>
       <c r="M19" t="n">
-        <v>0.149</v>
+        <v>-1.2377</v>
       </c>
       <c r="N19" t="n">
-        <v>0.149</v>
+        <v>-0.2193</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-1.0184</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0205</v>
+        <v>-0.6928</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.5984</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0205</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.9347</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. MOTOS CABODEVILLA</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3701</v>
+        <v>-0.4676</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4991</v>
+        <v>0.3697</v>
       </c>
       <c r="F20" t="n">
-        <v>0.129</v>
+        <v>-0.8373</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1697</v>
+        <v>-0.8411999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5053</v>
+        <v>-1.7393</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.675</v>
+        <v>0.8981</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.823</v>
+        <v>0.4586</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5141</v>
+        <v>-0.8419</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3371</v>
+        <v>1.3005</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6533</v>
+        <v>-1.2998</v>
       </c>
       <c r="N20" t="n">
-        <v>0.9912</v>
+        <v>-0.8974</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3379</v>
+        <v>-0.4024</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.418</v>
+        <v>0.0463</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1286</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5465</v>
+        <v>0.1352</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1952</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. ANSORREGUI DEBA</t>
+          <t>M. MOTOS CABODEVILLA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9415</v>
+        <v>-0.4947</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9535</v>
+        <v>-0.8344</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0121</v>
+        <v>0.3397</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4769</v>
+        <v>-0.1697</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7693</v>
+        <v>1.5053</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2463</v>
+        <v>-1.675</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7608</v>
+        <v>-0.823</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9886</v>
+        <v>0.5141</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.2279</v>
+        <v>-1.3371</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2377</v>
+        <v>0.6533</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2193</v>
+        <v>0.9912</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0184</v>
+        <v>-0.3379</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.2175</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3993</v>
+        <v>-0.5426</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.822</v>
+        <v>-0.2067</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5773</v>
+        <v>-0.3359</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9347</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0.1952</v>
       </c>
       <c r="X21" t="n">
-        <v>0.7395</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9486</v>
+        <v>-0.7688</v>
       </c>
       <c r="E22" t="n">
         <v>-0.7633</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1853</v>
+        <v>-0.0055</v>
       </c>
       <c r="G22" t="n">
         <v>0.1304</v>
@@ -2170,13 +2170,13 @@
         <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4265</v>
+        <v>-0.2466</v>
       </c>
       <c r="T22" t="n">
         <v>-0.3425</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.08400000000000001</v>
+        <v>0.0958</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7741</v>
+        <v>-2.4774</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1941</v>
+        <v>-1.0824</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.58</v>
+        <v>-1.395</v>
       </c>
       <c r="G23" t="n">
         <v>1.8857</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3548</v>
+        <v>-1.0581</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.548</v>
+        <v>-0.4362</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8068</v>
+        <v>-0.6219</v>
       </c>
       <c r="V23" t="n">
         <v>-1.13</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.605</v>
+        <v>-4.0733</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3372</v>
+        <v>-3.1137</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2678</v>
+        <v>-0.9596</v>
       </c>
       <c r="G24" t="n">
         <v>-1.1212</v>
@@ -2326,13 +2326,13 @@
         <v>1.7401</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.8086</v>
+        <v>-1.2768</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2329</v>
+        <v>-1.0094</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5756</v>
+        <v>-0.2674</v>
       </c>
       <c r="V24" t="n">
         <v>0.9347</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.2912</v>
+        <v>-4.9379</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.004</v>
+        <v>-1.8923</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.2871</v>
+        <v>-3.0457</v>
       </c>
       <c r="G25" t="n">
         <v>-3.0484</v>
@@ -2404,13 +2404,13 @@
         <v>1.0875</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0703</v>
+        <v>-0.7171</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.6417</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3169</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-2.2599</v>
@@ -2437,22 +2437,22 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.372199999999999</v>
+        <v>-4.881999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.446499999999999</v>
+        <v>0.4463999999999997</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.8187</v>
+        <v>-5.3287</v>
       </c>
       <c r="G26" t="n">
         <v>6.781</v>
       </c>
       <c r="H26" t="n">
-        <v>5.290699999999999</v>
+        <v>5.290700000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>1.490200000000001</v>
+        <v>1.4902</v>
       </c>
       <c r="J26" t="n">
         <v>15.0223</v>
@@ -2482,13 +2482,13 @@
         <v>10.8752</v>
       </c>
       <c r="S26" t="n">
-        <v>-10.3709</v>
+        <v>-8.8805</v>
       </c>
       <c r="T26" t="n">
-        <v>-6.609299999999999</v>
+        <v>-6.609100000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.7613</v>
+        <v>-2.2713</v>
       </c>
       <c r="V26" t="n">
         <v>-1.695</v>
